--- a/artfynd/A 7956-2022 artfynd.xlsx
+++ b/artfynd/A 7956-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7956-2022 artfynd.xlsx
+++ b/artfynd/A 7956-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111297892</v>
+        <v>112026357</v>
       </c>
       <c r="B2" t="n">
-        <v>89423</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nälkejärvi, Nb</t>
+          <t>Oksajärvi, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>816853.6881084231</v>
+        <v>817585</v>
       </c>
       <c r="R2" t="n">
-        <v>7525315.845139475</v>
+        <v>7525395</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,49 +768,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stefan Andersson, per-erik mukka, Robert Flygare</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112026615</v>
+        <v>112026454</v>
       </c>
       <c r="B3" t="n">
-        <v>90807</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817590</v>
+        <v>817560</v>
       </c>
       <c r="R3" t="n">
-        <v>7525376</v>
+        <v>7525355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,6 +882,1995 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112026562</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93213</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>817560</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7525340</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>112026264</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>817575</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7525535</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112026556</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93222</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellodon fuligineoalbus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>817560</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7525340</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112026312</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>817595</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7525465</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112026332</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>817605</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7525460</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112026409</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>817580</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7525385</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112026615</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>817590</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7525375</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112026382</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>817585</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7525395</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>112026417</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>817560</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7525360</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>112026558</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>817560</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7525340</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>112026596</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>817570</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7525295</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>112026246</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>817575</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7525570</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>112026600</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>817575</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7525295</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>112026306</v>
+      </c>
+      <c r="B17" t="n">
+        <v>90522</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>817575</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7525510</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>112026344</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90522</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>817585</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7525400</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>112026254</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>817575</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7525535</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>112026561</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Oksajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>817560</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7525340</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118974019</v>
+      </c>
+      <c r="B21" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>817274</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7525441</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118974077</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Laihajärvi, Laihajärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>817294</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7525413</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junosuando</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack i en asp.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7956-2022 artfynd.xlsx
+++ b/artfynd/A 7956-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026357</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026562</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026264</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026556</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1302,6 +1332,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026312</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026332</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1512,6 +1552,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026409</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026615</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1722,6 +1772,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026382</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1827,6 +1882,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026417</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026558</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2037,6 +2102,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026596</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2142,6 +2212,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026246</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2247,6 +2322,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026600</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2352,6 +2432,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026306</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2457,6 +2542,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026344</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2562,6 +2652,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026254</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2667,6 +2762,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112026561</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2764,6 +2864,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118974019</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2871,8 +2976,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118974077</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>